--- a/outputs/racisme/racisme_annotations_gold_flat.xlsx
+++ b/outputs/racisme/racisme_annotations_gold_flat.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,243 +413,253 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AU202"/>
+  <dimension ref="A1:AW202"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>idx</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>TIME</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>NAME</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>TEXT</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>ROLE</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>HATE</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>TARGET</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>VERBAL_ABUSE</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>INTENTION</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>CONTEXT</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>SENTIMENT</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Colère</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Dégoût</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Joie</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Peur</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Surprise</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Tristesse</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Admiration</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Culpabilité</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Embarras</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>Fierté</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>Jalousie</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Autre</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>reviewed</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>n_spans</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>spans_json</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>span1_text</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>span2_text</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>span3_text</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>span4_text</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>span1_cat</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>span2_cat</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>span3_cat</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>span4_cat</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>span1_mode</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>span2_mode</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>span3_mode</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <t>span4_mode</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AN1" t="inlineStr">
         <is>
           <t>n_disagreements</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AO1" t="inlineStr">
         <is>
           <t>Comportementale</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AP1" t="inlineStr">
         <is>
           <t>Désignée</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AQ1" t="inlineStr">
         <is>
           <t>Montrée</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="AR1" t="inlineStr">
         <is>
           <t>Suggérée</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="AS1" t="inlineStr">
         <is>
           <t>Emo</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="AT1" t="inlineStr">
         <is>
           <t>Base</t>
         </is>
       </c>
-      <c r="AU1" s="1" t="inlineStr">
+      <c r="AU1" t="inlineStr">
         <is>
           <t>Complexe</t>
+        </is>
+      </c>
+      <c r="AV1" t="inlineStr">
+        <is>
+          <t>typo</t>
+        </is>
+      </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>elongation</t>
         </is>
       </c>
     </row>
@@ -801,6 +799,12 @@
       <c r="AU2" t="n">
         <v>0</v>
       </c>
+      <c r="AV2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -954,6 +958,12 @@
       <c r="AU3" t="n">
         <v>1</v>
       </c>
+      <c r="AV3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1107,6 +1117,12 @@
       <c r="AU4" t="n">
         <v>0</v>
       </c>
+      <c r="AV4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1250,6 +1266,12 @@
         <v>1</v>
       </c>
       <c r="AU5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1385,6 +1407,12 @@
       <c r="AU6" t="n">
         <v>0</v>
       </c>
+      <c r="AV6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1548,6 +1576,12 @@
         <v>1</v>
       </c>
       <c r="AU7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1691,6 +1725,12 @@
       <c r="AU8" t="n">
         <v>0</v>
       </c>
+      <c r="AV8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1842,6 +1882,12 @@
         <v>0</v>
       </c>
       <c r="AU9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1977,6 +2023,12 @@
       <c r="AU10" t="n">
         <v>0</v>
       </c>
+      <c r="AV10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -2118,6 +2170,12 @@
       <c r="AU11" t="n">
         <v>0</v>
       </c>
+      <c r="AV11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -2247,6 +2305,12 @@
       <c r="AU12" t="n">
         <v>0</v>
       </c>
+      <c r="AV12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2398,6 +2462,12 @@
         <v>1</v>
       </c>
       <c r="AU13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2533,6 +2603,12 @@
       <c r="AU14" t="n">
         <v>0</v>
       </c>
+      <c r="AV14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2674,6 +2750,12 @@
       <c r="AU15" t="n">
         <v>0</v>
       </c>
+      <c r="AV15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2807,6 +2889,12 @@
       <c r="AU16" t="n">
         <v>0</v>
       </c>
+      <c r="AV16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2958,6 +3046,12 @@
         <v>1</v>
       </c>
       <c r="AU17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW17" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3093,6 +3187,12 @@
       <c r="AU18" t="n">
         <v>0</v>
       </c>
+      <c r="AV18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -3222,6 +3322,12 @@
       <c r="AU19" t="n">
         <v>0</v>
       </c>
+      <c r="AV19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -3353,6 +3459,12 @@
         <v>0</v>
       </c>
       <c r="AU20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW20" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3496,6 +3608,12 @@
       <c r="AU21" t="n">
         <v>0</v>
       </c>
+      <c r="AV21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3625,6 +3743,12 @@
       <c r="AU22" t="n">
         <v>0</v>
       </c>
+      <c r="AV22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3766,6 +3890,12 @@
       <c r="AU23" t="n">
         <v>0</v>
       </c>
+      <c r="AV23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3917,6 +4047,12 @@
         <v>1</v>
       </c>
       <c r="AU24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW24" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4048,6 +4184,12 @@
       <c r="AU25" t="n">
         <v>0</v>
       </c>
+      <c r="AV25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -4201,6 +4343,12 @@
       <c r="AU26" t="n">
         <v>0</v>
       </c>
+      <c r="AV26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -4364,6 +4512,12 @@
         <v>1</v>
       </c>
       <c r="AU27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW27" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4507,6 +4661,12 @@
       <c r="AU28" t="n">
         <v>0</v>
       </c>
+      <c r="AV28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW28" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -4648,6 +4808,12 @@
       <c r="AU29" t="n">
         <v>0</v>
       </c>
+      <c r="AV29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW29" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -4801,6 +4967,12 @@
       <c r="AU30" t="n">
         <v>0</v>
       </c>
+      <c r="AV30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW30" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4964,6 +5136,12 @@
         <v>1</v>
       </c>
       <c r="AU31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW31" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5119,6 +5297,12 @@
       <c r="AU32" t="n">
         <v>0</v>
       </c>
+      <c r="AV32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW32" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -5270,6 +5454,12 @@
         <v>1</v>
       </c>
       <c r="AU33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW33" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5413,6 +5603,12 @@
       <c r="AU34" t="n">
         <v>0</v>
       </c>
+      <c r="AV34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW34" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -5554,6 +5750,12 @@
       <c r="AU35" t="n">
         <v>0</v>
       </c>
+      <c r="AV35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW35" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -5707,6 +5909,12 @@
       <c r="AU36" t="n">
         <v>0</v>
       </c>
+      <c r="AV36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW36" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -5883,6 +6091,12 @@
       </c>
       <c r="AU37" t="n">
         <v>0</v>
+      </c>
+      <c r="AV37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW37" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -6021,6 +6235,12 @@
       <c r="AU38" t="n">
         <v>0</v>
       </c>
+      <c r="AV38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW38" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -6162,6 +6382,12 @@
       <c r="AU39" t="n">
         <v>0</v>
       </c>
+      <c r="AV39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW39" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -6299,6 +6525,12 @@
       <c r="AU40" t="n">
         <v>0</v>
       </c>
+      <c r="AV40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW40" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -6428,6 +6660,12 @@
       <c r="AU41" t="n">
         <v>0</v>
       </c>
+      <c r="AV41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW41" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -6581,6 +6819,12 @@
       <c r="AU42" t="n">
         <v>0</v>
       </c>
+      <c r="AV42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW42" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -6734,6 +6978,12 @@
       <c r="AU43" t="n">
         <v>0</v>
       </c>
+      <c r="AV43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW43" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -6897,6 +7147,12 @@
         <v>1</v>
       </c>
       <c r="AU44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW44" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7040,6 +7296,12 @@
       <c r="AU45" t="n">
         <v>0</v>
       </c>
+      <c r="AV45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW45" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -7181,6 +7443,12 @@
       <c r="AU46" t="n">
         <v>0</v>
       </c>
+      <c r="AV46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW46" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -7322,6 +7590,12 @@
       <c r="AU47" t="n">
         <v>0</v>
       </c>
+      <c r="AV47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW47" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -7463,6 +7737,12 @@
       <c r="AU48" t="n">
         <v>0</v>
       </c>
+      <c r="AV48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW48" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -7614,6 +7894,12 @@
         <v>1</v>
       </c>
       <c r="AU49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW49" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7757,6 +8043,12 @@
       <c r="AU50" t="n">
         <v>0</v>
       </c>
+      <c r="AV50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW50" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -7898,6 +8190,12 @@
       <c r="AU51" t="n">
         <v>0</v>
       </c>
+      <c r="AV51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW51" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -8049,6 +8347,12 @@
         <v>1</v>
       </c>
       <c r="AU52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW52" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8184,6 +8488,12 @@
       <c r="AU53" t="n">
         <v>0</v>
       </c>
+      <c r="AV53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW53" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -8325,6 +8635,12 @@
       <c r="AU54" t="n">
         <v>0</v>
       </c>
+      <c r="AV54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW54" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -8466,6 +8782,12 @@
       <c r="AU55" t="n">
         <v>0</v>
       </c>
+      <c r="AV55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW55" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -8619,6 +8941,12 @@
       <c r="AU56" t="n">
         <v>0</v>
       </c>
+      <c r="AV56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW56" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -8772,6 +9100,12 @@
       <c r="AU57" t="n">
         <v>0</v>
       </c>
+      <c r="AV57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW57" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -8911,6 +9245,12 @@
         <v>1</v>
       </c>
       <c r="AU58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW58" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9054,6 +9394,12 @@
       <c r="AU59" t="n">
         <v>0</v>
       </c>
+      <c r="AV59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW59" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -9207,6 +9553,12 @@
       <c r="AU60" t="n">
         <v>0</v>
       </c>
+      <c r="AV60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW60" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -9372,6 +9724,12 @@
       <c r="AU61" t="n">
         <v>0</v>
       </c>
+      <c r="AV61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW61" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -9525,6 +9883,12 @@
       <c r="AU62" t="n">
         <v>0</v>
       </c>
+      <c r="AV62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW62" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -9666,6 +10030,12 @@
       <c r="AU63" t="n">
         <v>0</v>
       </c>
+      <c r="AV63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW63" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -9819,6 +10189,12 @@
       <c r="AU64" t="n">
         <v>0</v>
       </c>
+      <c r="AV64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW64" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -9984,6 +10360,12 @@
       <c r="AU65" t="n">
         <v>0</v>
       </c>
+      <c r="AV65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW65" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -10149,6 +10531,12 @@
       <c r="AU66" t="n">
         <v>0</v>
       </c>
+      <c r="AV66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW66" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -10310,6 +10698,12 @@
       <c r="AU67" t="n">
         <v>0</v>
       </c>
+      <c r="AV67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW67" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -10455,6 +10849,12 @@
       <c r="AU68" t="n">
         <v>0</v>
       </c>
+      <c r="AV68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW68" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -10620,6 +11020,12 @@
       <c r="AU69" t="n">
         <v>0</v>
       </c>
+      <c r="AV69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW69" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -10763,6 +11169,12 @@
         <v>1</v>
       </c>
       <c r="AU70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW70" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10898,6 +11310,12 @@
       <c r="AU71" t="n">
         <v>0</v>
       </c>
+      <c r="AV71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW71" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -11049,6 +11467,12 @@
         <v>1</v>
       </c>
       <c r="AU72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW72" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11184,6 +11608,12 @@
       <c r="AU73" t="n">
         <v>0</v>
       </c>
+      <c r="AV73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW73" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -11337,6 +11767,12 @@
       <c r="AU74" t="n">
         <v>0</v>
       </c>
+      <c r="AV74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW74" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -11480,6 +11916,12 @@
         <v>1</v>
       </c>
       <c r="AU75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW75" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11615,6 +12057,12 @@
       <c r="AU76" t="n">
         <v>0</v>
       </c>
+      <c r="AV76" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW76" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -11748,6 +12196,12 @@
       <c r="AU77" t="n">
         <v>0</v>
       </c>
+      <c r="AV77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW77" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -11913,6 +12367,12 @@
       <c r="AU78" t="n">
         <v>0</v>
       </c>
+      <c r="AV78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW78" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -12064,6 +12524,12 @@
         <v>1</v>
       </c>
       <c r="AU79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW79" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12199,6 +12665,12 @@
       <c r="AU80" t="n">
         <v>0</v>
       </c>
+      <c r="AV80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW80" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -12352,6 +12824,12 @@
       <c r="AU81" t="n">
         <v>0</v>
       </c>
+      <c r="AV81" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW81" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -12503,6 +12981,12 @@
         <v>1</v>
       </c>
       <c r="AU82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW82" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12646,6 +13130,12 @@
       <c r="AU83" t="n">
         <v>0</v>
       </c>
+      <c r="AV83" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW83" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -12803,6 +13293,12 @@
       <c r="AU84" t="n">
         <v>0</v>
       </c>
+      <c r="AV84" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW84" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -12954,6 +13450,12 @@
         <v>1</v>
       </c>
       <c r="AU85" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV85" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW85" t="n">
         <v>0</v>
       </c>
     </row>
@@ -13089,6 +13591,12 @@
       <c r="AU86" t="n">
         <v>0</v>
       </c>
+      <c r="AV86" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW86" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -13222,6 +13730,12 @@
       <c r="AU87" t="n">
         <v>0</v>
       </c>
+      <c r="AV87" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW87" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -13355,6 +13869,12 @@
       <c r="AU88" t="n">
         <v>0</v>
       </c>
+      <c r="AV88" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW88" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -13488,6 +14008,12 @@
       <c r="AU89" t="n">
         <v>0</v>
       </c>
+      <c r="AV89" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW89" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -13621,6 +14147,12 @@
       <c r="AU90" t="n">
         <v>0</v>
       </c>
+      <c r="AV90" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW90" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -13754,6 +14286,12 @@
       <c r="AU91" t="n">
         <v>0</v>
       </c>
+      <c r="AV91" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW91" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -13887,6 +14425,12 @@
       <c r="AU92" t="n">
         <v>0</v>
       </c>
+      <c r="AV92" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW92" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -14028,6 +14572,12 @@
       <c r="AU93" t="n">
         <v>0</v>
       </c>
+      <c r="AV93" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW93" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -14179,6 +14729,12 @@
         <v>1</v>
       </c>
       <c r="AU94" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV94" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW94" t="n">
         <v>0</v>
       </c>
     </row>
@@ -14320,6 +14876,12 @@
         <v>0</v>
       </c>
       <c r="AU95" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV95" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW95" t="n">
         <v>0</v>
       </c>
     </row>
@@ -14455,6 +15017,12 @@
       <c r="AU96" t="n">
         <v>0</v>
       </c>
+      <c r="AV96" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW96" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -14584,6 +15152,12 @@
       <c r="AU97" t="n">
         <v>0</v>
       </c>
+      <c r="AV97" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW97" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -14717,6 +15291,12 @@
       <c r="AU98" t="n">
         <v>0</v>
       </c>
+      <c r="AV98" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW98" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -14850,6 +15430,12 @@
       <c r="AU99" t="n">
         <v>0</v>
       </c>
+      <c r="AV99" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW99" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -14981,6 +15567,12 @@
         <v>0</v>
       </c>
       <c r="AU100" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV100" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW100" t="n">
         <v>0</v>
       </c>
     </row>
@@ -15112,6 +15704,12 @@
       <c r="AU101" t="n">
         <v>0</v>
       </c>
+      <c r="AV101" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW101" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -15263,6 +15861,12 @@
         <v>1</v>
       </c>
       <c r="AU102" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV102" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW102" t="n">
         <v>0</v>
       </c>
     </row>
@@ -15398,6 +16002,12 @@
       <c r="AU103" t="n">
         <v>0</v>
       </c>
+      <c r="AV103" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW103" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -15543,6 +16153,12 @@
       <c r="AU104" t="n">
         <v>0</v>
       </c>
+      <c r="AV104" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW104" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -15704,6 +16320,12 @@
       <c r="AU105" t="n">
         <v>0</v>
       </c>
+      <c r="AV105" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW105" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -15843,6 +16465,12 @@
         <v>1</v>
       </c>
       <c r="AU106" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV106" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW106" t="n">
         <v>0</v>
       </c>
     </row>
@@ -15978,6 +16606,12 @@
       <c r="AU107" t="n">
         <v>0</v>
       </c>
+      <c r="AV107" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW107" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -16131,6 +16765,12 @@
       <c r="AU108" t="n">
         <v>0</v>
       </c>
+      <c r="AV108" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW108" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -16294,6 +16934,12 @@
         <v>1</v>
       </c>
       <c r="AU109" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV109" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW109" t="n">
         <v>0</v>
       </c>
     </row>
@@ -16437,6 +17083,12 @@
       <c r="AU110" t="n">
         <v>0</v>
       </c>
+      <c r="AV110" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW110" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -16570,6 +17222,12 @@
       <c r="AU111" t="n">
         <v>0</v>
       </c>
+      <c r="AV111" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW111" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -16711,6 +17369,12 @@
       <c r="AU112" t="n">
         <v>0</v>
       </c>
+      <c r="AV112" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW112" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -16864,6 +17528,12 @@
       <c r="AU113" t="n">
         <v>0</v>
       </c>
+      <c r="AV113" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW113" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -17019,6 +17689,12 @@
         <v>1</v>
       </c>
       <c r="AU114" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV114" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW114" t="n">
         <v>0</v>
       </c>
     </row>
@@ -17162,6 +17838,12 @@
       <c r="AU115" t="n">
         <v>0</v>
       </c>
+      <c r="AV115" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW115" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -17314,6 +17996,12 @@
       </c>
       <c r="AU116" t="n">
         <v>0</v>
+      </c>
+      <c r="AV116" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW116" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="117">
@@ -17456,6 +18144,12 @@
       <c r="AU117" t="n">
         <v>0</v>
       </c>
+      <c r="AV117" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -17617,6 +18311,12 @@
       <c r="AU118" t="n">
         <v>0</v>
       </c>
+      <c r="AV118" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -17768,6 +18468,12 @@
         <v>1</v>
       </c>
       <c r="AU119" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW119" t="n">
         <v>0</v>
       </c>
     </row>
@@ -17921,6 +18627,12 @@
         <v>1</v>
       </c>
       <c r="AU120" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW120" t="n">
         <v>0</v>
       </c>
     </row>
@@ -18064,6 +18776,12 @@
       <c r="AU121" t="n">
         <v>0</v>
       </c>
+      <c r="AV121" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -18219,6 +18937,12 @@
         <v>1</v>
       </c>
       <c r="AU122" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW122" t="n">
         <v>0</v>
       </c>
     </row>
@@ -18362,6 +19086,12 @@
       <c r="AU123" t="n">
         <v>0</v>
       </c>
+      <c r="AV123" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -18513,6 +19243,12 @@
         <v>1</v>
       </c>
       <c r="AU124" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW124" t="n">
         <v>0</v>
       </c>
     </row>
@@ -18656,6 +19392,12 @@
       <c r="AU125" t="n">
         <v>0</v>
       </c>
+      <c r="AV125" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -18797,6 +19539,12 @@
       <c r="AU126" t="n">
         <v>0</v>
       </c>
+      <c r="AV126" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -18938,6 +19686,12 @@
       <c r="AU127" t="n">
         <v>0</v>
       </c>
+      <c r="AV127" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -19091,6 +19845,12 @@
       <c r="AU128" t="n">
         <v>0</v>
       </c>
+      <c r="AV128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -19244,6 +20004,12 @@
       <c r="AU129" t="n">
         <v>0</v>
       </c>
+      <c r="AV129" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -19421,6 +20187,12 @@
       <c r="AU130" t="n">
         <v>0</v>
       </c>
+      <c r="AV130" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -19574,6 +20346,12 @@
       <c r="AU131" t="n">
         <v>0</v>
       </c>
+      <c r="AV131" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -19727,6 +20505,12 @@
       <c r="AU132" t="n">
         <v>0</v>
       </c>
+      <c r="AV132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -19872,6 +20656,12 @@
       <c r="AU133" t="n">
         <v>0</v>
       </c>
+      <c r="AV133" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -20019,6 +20809,12 @@
         <v>1</v>
       </c>
       <c r="AU134" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW134" t="n">
         <v>0</v>
       </c>
     </row>
@@ -20162,6 +20958,12 @@
       <c r="AU135" t="n">
         <v>0</v>
       </c>
+      <c r="AV135" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -20313,6 +21115,12 @@
         <v>0</v>
       </c>
       <c r="AU136" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW136" t="n">
         <v>0</v>
       </c>
     </row>
@@ -20456,6 +21264,12 @@
       <c r="AU137" t="n">
         <v>0</v>
       </c>
+      <c r="AV137" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -20607,6 +21421,12 @@
         <v>1</v>
       </c>
       <c r="AU138" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW138" t="n">
         <v>0</v>
       </c>
     </row>
@@ -20742,6 +21562,12 @@
       <c r="AU139" t="n">
         <v>0</v>
       </c>
+      <c r="AV139" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -20883,6 +21709,12 @@
       <c r="AU140" t="n">
         <v>0</v>
       </c>
+      <c r="AV140" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -21070,6 +21902,12 @@
         <v>1</v>
       </c>
       <c r="AU141" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW141" t="n">
         <v>0</v>
       </c>
     </row>
@@ -21213,6 +22051,12 @@
       <c r="AU142" t="n">
         <v>0</v>
       </c>
+      <c r="AV142" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -21358,6 +22202,12 @@
       <c r="AU143" t="n">
         <v>0</v>
       </c>
+      <c r="AV143" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -21505,6 +22355,12 @@
         <v>1</v>
       </c>
       <c r="AU144" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV144" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW144" t="n">
         <v>0</v>
       </c>
     </row>
@@ -21638,6 +22494,12 @@
         <v>0</v>
       </c>
       <c r="AU145" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV145" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW145" t="n">
         <v>0</v>
       </c>
     </row>
@@ -21781,6 +22643,12 @@
       <c r="AU146" t="n">
         <v>0</v>
       </c>
+      <c r="AV146" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW146" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -21918,6 +22786,12 @@
       <c r="AU147" t="n">
         <v>0</v>
       </c>
+      <c r="AV147" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW147" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -22081,6 +22955,12 @@
         <v>1</v>
       </c>
       <c r="AU148" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV148" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW148" t="n">
         <v>0</v>
       </c>
     </row>
@@ -22224,6 +23104,12 @@
       <c r="AU149" t="n">
         <v>0</v>
       </c>
+      <c r="AV149" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW149" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -22365,6 +23251,12 @@
       <c r="AU150" t="n">
         <v>0</v>
       </c>
+      <c r="AV150" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW150" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -22518,6 +23410,12 @@
       <c r="AU151" t="n">
         <v>0</v>
       </c>
+      <c r="AV151" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW151" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -22662,6 +23560,12 @@
       </c>
       <c r="AU152" t="n">
         <v>1</v>
+      </c>
+      <c r="AV152" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW152" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="153">
@@ -22804,6 +23708,12 @@
       <c r="AU153" t="n">
         <v>0</v>
       </c>
+      <c r="AV153" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW153" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -22955,6 +23865,12 @@
         <v>1</v>
       </c>
       <c r="AU154" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV154" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW154" t="n">
         <v>0</v>
       </c>
     </row>
@@ -23098,6 +24014,12 @@
       <c r="AU155" t="n">
         <v>0</v>
       </c>
+      <c r="AV155" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW155" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -23261,6 +24183,12 @@
         <v>1</v>
       </c>
       <c r="AU156" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV156" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW156" t="n">
         <v>0</v>
       </c>
     </row>
@@ -23404,6 +24332,12 @@
       <c r="AU157" t="n">
         <v>0</v>
       </c>
+      <c r="AV157" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW157" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -23557,6 +24491,12 @@
       <c r="AU158" t="n">
         <v>1</v>
       </c>
+      <c r="AV158" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW158" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -23710,6 +24650,12 @@
       <c r="AU159" t="n">
         <v>0</v>
       </c>
+      <c r="AV159" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW159" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -23854,6 +24800,12 @@
       </c>
       <c r="AU160" t="n">
         <v>0</v>
+      </c>
+      <c r="AV160" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW160" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="161">
@@ -23996,6 +24948,12 @@
       <c r="AU161" t="n">
         <v>0</v>
       </c>
+      <c r="AV161" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW161" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -24137,6 +25095,12 @@
       <c r="AU162" t="n">
         <v>0</v>
       </c>
+      <c r="AV162" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW162" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -24288,6 +25252,12 @@
         <v>1</v>
       </c>
       <c r="AU163" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV163" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW163" t="n">
         <v>0</v>
       </c>
     </row>
@@ -24431,6 +25401,12 @@
       <c r="AU164" t="n">
         <v>0</v>
       </c>
+      <c r="AV164" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW164" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -24564,6 +25540,12 @@
       <c r="AU165" t="n">
         <v>0</v>
       </c>
+      <c r="AV165" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW165" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -24716,6 +25698,12 @@
       </c>
       <c r="AU166" t="n">
         <v>0</v>
+      </c>
+      <c r="AV166" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW166" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="167">
@@ -24858,6 +25846,12 @@
       <c r="AU167" t="n">
         <v>0</v>
       </c>
+      <c r="AV167" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW167" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -25009,6 +26003,12 @@
         <v>1</v>
       </c>
       <c r="AU168" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV168" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW168" t="n">
         <v>0</v>
       </c>
     </row>
@@ -25164,6 +26164,12 @@
       <c r="AU169" t="n">
         <v>0</v>
       </c>
+      <c r="AV169" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW169" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -25317,6 +26323,12 @@
       <c r="AU170" t="n">
         <v>0</v>
       </c>
+      <c r="AV170" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW170" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -25470,6 +26482,12 @@
       <c r="AU171" t="n">
         <v>0</v>
       </c>
+      <c r="AV171" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW171" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -25621,6 +26639,12 @@
         <v>1</v>
       </c>
       <c r="AU172" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV172" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW172" t="n">
         <v>0</v>
       </c>
     </row>
@@ -25752,6 +26776,12 @@
       <c r="AU173" t="n">
         <v>0</v>
       </c>
+      <c r="AV173" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW173" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
@@ -25899,6 +26929,12 @@
         <v>1</v>
       </c>
       <c r="AU174" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV174" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW174" t="n">
         <v>0</v>
       </c>
     </row>
@@ -26042,6 +27078,12 @@
       <c r="AU175" t="n">
         <v>0</v>
       </c>
+      <c r="AV175" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW175" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
@@ -26183,6 +27225,12 @@
       <c r="AU176" t="n">
         <v>0</v>
       </c>
+      <c r="AV176" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW176" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
@@ -26324,6 +27372,12 @@
       <c r="AU177" t="n">
         <v>0</v>
       </c>
+      <c r="AV177" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW177" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
@@ -26465,6 +27519,12 @@
       <c r="AU178" t="n">
         <v>0</v>
       </c>
+      <c r="AV178" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW178" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
@@ -26628,6 +27688,12 @@
         <v>1</v>
       </c>
       <c r="AU179" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV179" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW179" t="n">
         <v>0</v>
       </c>
     </row>
@@ -26759,6 +27825,12 @@
       <c r="AU180" t="n">
         <v>0</v>
       </c>
+      <c r="AV180" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW180" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
@@ -26922,6 +27994,12 @@
         <v>1</v>
       </c>
       <c r="AU181" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV181" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW181" t="n">
         <v>0</v>
       </c>
     </row>
@@ -27065,6 +28143,12 @@
       <c r="AU182" t="n">
         <v>0</v>
       </c>
+      <c r="AV182" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW182" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
@@ -27216,6 +28300,12 @@
         <v>1</v>
       </c>
       <c r="AU183" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV183" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW183" t="n">
         <v>0</v>
       </c>
     </row>
@@ -27367,6 +28457,12 @@
       <c r="AU184" t="n">
         <v>1</v>
       </c>
+      <c r="AV184" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW184" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
@@ -27530,6 +28626,12 @@
         <v>1</v>
       </c>
       <c r="AU185" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV185" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW185" t="n">
         <v>0</v>
       </c>
     </row>
@@ -27673,6 +28775,12 @@
       <c r="AU186" t="n">
         <v>0</v>
       </c>
+      <c r="AV186" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW186" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
@@ -27816,6 +28924,12 @@
         <v>1</v>
       </c>
       <c r="AU187" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV187" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW187" t="n">
         <v>0</v>
       </c>
     </row>
@@ -27959,6 +29073,12 @@
       <c r="AU188" t="n">
         <v>0</v>
       </c>
+      <c r="AV188" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW188" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
@@ -28088,6 +29208,12 @@
       <c r="AU189" t="n">
         <v>0</v>
       </c>
+      <c r="AV189" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW189" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
@@ -28241,6 +29367,12 @@
       <c r="AU190" t="n">
         <v>0</v>
       </c>
+      <c r="AV190" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW190" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
@@ -28388,6 +29520,12 @@
         <v>1</v>
       </c>
       <c r="AU191" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV191" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW191" t="n">
         <v>0</v>
       </c>
     </row>
@@ -28531,6 +29669,12 @@
       <c r="AU192" t="n">
         <v>0</v>
       </c>
+      <c r="AV192" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW192" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
@@ -28684,6 +29828,12 @@
       <c r="AU193" t="n">
         <v>0</v>
       </c>
+      <c r="AV193" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW193" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
@@ -28835,6 +29985,12 @@
         <v>0</v>
       </c>
       <c r="AU194" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV194" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW194" t="n">
         <v>0</v>
       </c>
     </row>
@@ -28970,6 +30126,12 @@
       <c r="AU195" t="n">
         <v>0</v>
       </c>
+      <c r="AV195" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW195" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
@@ -29113,6 +30275,12 @@
         <v>1</v>
       </c>
       <c r="AU196" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV196" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW196" t="n">
         <v>0</v>
       </c>
     </row>
@@ -29248,6 +30416,12 @@
       <c r="AU197" t="n">
         <v>0</v>
       </c>
+      <c r="AV197" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW197" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
@@ -29425,6 +30599,12 @@
       <c r="AU198" t="n">
         <v>0</v>
       </c>
+      <c r="AV198" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW198" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
@@ -29570,6 +30750,12 @@
       <c r="AU199" t="n">
         <v>0</v>
       </c>
+      <c r="AV199" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW199" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
@@ -29721,6 +30907,12 @@
         <v>1</v>
       </c>
       <c r="AU200" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV200" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW200" t="n">
         <v>0</v>
       </c>
     </row>
@@ -29864,6 +31056,12 @@
       <c r="AU201" t="n">
         <v>0</v>
       </c>
+      <c r="AV201" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW201" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
@@ -30017,6 +31215,12 @@
       <c r="AU202" t="n">
         <v>0</v>
       </c>
+      <c r="AV202" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW202" t="n">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
